--- a/results/01_pollution_assessment/tables/SumRel_site_rankings.xlsx
+++ b/results/01_pollution_assessment/tables/SumRel_site_rankings.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.267377728946281</v>
+        <v>1.267377728946282</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.41959144276309</v>
+        <v>1.419591442763091</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.480325127657849</v>
+        <v>1.48032512765785</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.587931943698385</v>
+        <v>1.587931943698386</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.592799680919376</v>
+        <v>1.592799680919377</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.599903870452274</v>
+        <v>1.599903870452275</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.635376515132371</v>
+        <v>1.635376515132372</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.65972121560007</v>
+        <v>1.659721215600071</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.68255615038818</v>
+        <v>1.682556150388181</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.686067623874442</v>
+        <v>1.686067623874443</v>
       </c>
       <c r="D14" t="n">
         <v>13</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.697702529447634</v>
+        <v>1.697702529447635</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.712674570899483</v>
+        <v>1.712674570899484</v>
       </c>
       <c r="D18" t="n">
         <v>17</v>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.719081411373789</v>
+        <v>1.71908141137379</v>
       </c>
       <c r="D19" t="n">
         <v>18</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.720354307325032</v>
+        <v>1.720354307325034</v>
       </c>
       <c r="D20" t="n">
         <v>19</v>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.740118668200615</v>
+        <v>1.740118668200616</v>
       </c>
       <c r="D22" t="n">
         <v>21</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.749005322801854</v>
+        <v>1.749005322801855</v>
       </c>
       <c r="D23" t="n">
         <v>22</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.757680422973135</v>
+        <v>1.757680422973136</v>
       </c>
       <c r="D25" t="n">
         <v>24</v>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.765264470594877</v>
+        <v>1.765264470594878</v>
       </c>
       <c r="D26" t="n">
         <v>25</v>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.77136061975014</v>
+        <v>1.771360619750141</v>
       </c>
       <c r="D27" t="n">
         <v>26</v>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.781367992902675</v>
+        <v>1.781367992902676</v>
       </c>
       <c r="D28" t="n">
         <v>27</v>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.814015012552385</v>
+        <v>1.814015012552386</v>
       </c>
       <c r="D29" t="n">
         <v>28</v>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.819100764139649</v>
+        <v>1.81910076413965</v>
       </c>
       <c r="D31" t="n">
         <v>30</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.8264396881881</v>
+        <v>1.826439688188101</v>
       </c>
       <c r="D33" t="n">
         <v>32</v>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1.83509232946154</v>
+        <v>1.835092329461541</v>
       </c>
       <c r="D34" t="n">
         <v>33</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.840548077590976</v>
+        <v>1.840548077590977</v>
       </c>
       <c r="D35" t="n">
         <v>34</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.850380323804276</v>
+        <v>1.850380323804277</v>
       </c>
       <c r="D36" t="n">
         <v>35</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.856580591721243</v>
+        <v>1.856580591721244</v>
       </c>
       <c r="D38" t="n">
         <v>37</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.874231056252467</v>
+        <v>1.874231056252468</v>
       </c>
       <c r="D41" t="n">
         <v>40</v>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.882490492086886</v>
+        <v>1.882490492086887</v>
       </c>
       <c r="D42" t="n">
         <v>41</v>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.887965471466098</v>
+        <v>1.887965471466099</v>
       </c>
       <c r="D43" t="n">
         <v>42</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.921488818329889</v>
+        <v>1.92148881832989</v>
       </c>
       <c r="D44" t="n">
         <v>43</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.924241807834034</v>
+        <v>1.924241807834035</v>
       </c>
       <c r="D46" t="n">
         <v>45</v>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.940391299795311</v>
+        <v>1.940391299795312</v>
       </c>
       <c r="D47" t="n">
         <v>46</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.946827249585245</v>
+        <v>1.946827249585246</v>
       </c>
       <c r="D50" t="n">
         <v>49</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.956132481892578</v>
+        <v>1.95613248189258</v>
       </c>
       <c r="D51" t="n">
         <v>50</v>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.95637328929545</v>
+        <v>1.956373289295451</v>
       </c>
       <c r="D52" t="n">
         <v>51</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.958286583401054</v>
+        <v>1.958286583401055</v>
       </c>
       <c r="D54" t="n">
         <v>53</v>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.962270156315282</v>
+        <v>1.962270156315283</v>
       </c>
       <c r="D55" t="n">
         <v>54</v>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.963913055496472</v>
+        <v>1.963913055496473</v>
       </c>
       <c r="D56" t="n">
         <v>55</v>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.96579890939884</v>
+        <v>1.965798909398841</v>
       </c>
       <c r="D58" t="n">
         <v>57</v>
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.967550286873326</v>
+        <v>1.967550286873327</v>
       </c>
       <c r="D59" t="n">
         <v>58</v>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.969973419804847</v>
+        <v>1.969973419804848</v>
       </c>
       <c r="D60" t="n">
         <v>59</v>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.974536741320473</v>
+        <v>1.974536741320474</v>
       </c>
       <c r="D61" t="n">
         <v>60</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1.980061994995101</v>
+        <v>1.980061994995102</v>
       </c>
       <c r="D62" t="n">
         <v>61</v>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1.98659095328797</v>
+        <v>1.986590953287971</v>
       </c>
       <c r="D63" t="n">
         <v>62</v>
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1.991911662371239</v>
+        <v>1.99191166237124</v>
       </c>
       <c r="D64" t="n">
         <v>63</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1.996299924242431</v>
+        <v>1.996299924242432</v>
       </c>
       <c r="D65" t="n">
         <v>64</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2.001663093756192</v>
+        <v>2.001663093756193</v>
       </c>
       <c r="D66" t="n">
         <v>65</v>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2.024602947540684</v>
+        <v>2.024602947540685</v>
       </c>
       <c r="D68" t="n">
         <v>67</v>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2.026284898920165</v>
+        <v>2.026284898920166</v>
       </c>
       <c r="D69" t="n">
         <v>68</v>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2.030724447306778</v>
+        <v>2.030724447306779</v>
       </c>
       <c r="D70" t="n">
         <v>69</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2.034841982253901</v>
+        <v>2.034841982253903</v>
       </c>
       <c r="D71" t="n">
         <v>70</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2.035944702964898</v>
+        <v>2.035944702964899</v>
       </c>
       <c r="D72" t="n">
         <v>71</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2.04393451113358</v>
+        <v>2.043934511133581</v>
       </c>
       <c r="D74" t="n">
         <v>73</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2.051094598265961</v>
+        <v>2.051094598265962</v>
       </c>
       <c r="D75" t="n">
         <v>74</v>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2.0511564272528</v>
+        <v>2.051156427252802</v>
       </c>
       <c r="D76" t="n">
         <v>75</v>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2.083872627006261</v>
+        <v>2.083872627006262</v>
       </c>
       <c r="D79" t="n">
         <v>78</v>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2.084703800191285</v>
+        <v>2.084703800191287</v>
       </c>
       <c r="D80" t="n">
         <v>79</v>
@@ -1719,7 +1719,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2.089634443137524</v>
+        <v>2.089634443137526</v>
       </c>
       <c r="D81" t="n">
         <v>80</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2.093341844944755</v>
+        <v>2.093341844944756</v>
       </c>
       <c r="D83" t="n">
         <v>82</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2.096273428956862</v>
+        <v>2.096273428956863</v>
       </c>
       <c r="D84" t="n">
         <v>83</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2.105429015772428</v>
+        <v>2.105429015772427</v>
       </c>
       <c r="D86" t="n">
         <v>85</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2.122204256854241</v>
+        <v>2.122204256854243</v>
       </c>
       <c r="D90" t="n">
         <v>89</v>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2.136736479757284</v>
+        <v>2.136736479757285</v>
       </c>
       <c r="D93" t="n">
         <v>92</v>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2.142038247198994</v>
+        <v>2.142038247198995</v>
       </c>
       <c r="D94" t="n">
         <v>93</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2.160574503947267</v>
+        <v>2.160574503947268</v>
       </c>
       <c r="D97" t="n">
         <v>96</v>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2.166886998732811</v>
+        <v>2.166886998732812</v>
       </c>
       <c r="D99" t="n">
         <v>98</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2.167399578748308</v>
+        <v>2.16739957874831</v>
       </c>
       <c r="D100" t="n">
         <v>99</v>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2.179427979287093</v>
+        <v>2.179427979287095</v>
       </c>
       <c r="D102" t="n">
         <v>101</v>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2.189717478082502</v>
+        <v>2.189717478082504</v>
       </c>
       <c r="D103" t="n">
         <v>102</v>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2.190325534865725</v>
+        <v>2.190325534865726</v>
       </c>
       <c r="D104" t="n">
         <v>103</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2.197833998920958</v>
+        <v>2.197833998920959</v>
       </c>
       <c r="D105" t="n">
         <v>104</v>
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2.199079042961261</v>
+        <v>2.199079042961262</v>
       </c>
       <c r="D106" t="n">
         <v>105</v>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2.19947907359759</v>
+        <v>2.199479073597591</v>
       </c>
       <c r="D107" t="n">
         <v>106</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2.203189639917697</v>
+        <v>2.203189639917696</v>
       </c>
       <c r="D108" t="n">
         <v>107</v>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2.211204947752738</v>
+        <v>2.211204947752739</v>
       </c>
       <c r="D109" t="n">
         <v>108</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2.223126384917812</v>
+        <v>2.223126384917813</v>
       </c>
       <c r="D112" t="n">
         <v>111</v>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2.223387786056885</v>
+        <v>2.223387786056886</v>
       </c>
       <c r="D113" t="n">
         <v>112</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2.263291402362695</v>
+        <v>2.263291402362696</v>
       </c>
       <c r="D121" t="n">
         <v>120</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2.280966722486821</v>
+        <v>2.280966722486822</v>
       </c>
       <c r="D123" t="n">
         <v>122</v>
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2.284717445377044</v>
+        <v>2.284717445377045</v>
       </c>
       <c r="D125" t="n">
         <v>124</v>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2.286760865150849</v>
+        <v>2.286760865150848</v>
       </c>
       <c r="D126" t="n">
         <v>125</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2.291570420175599</v>
+        <v>2.2915704201756</v>
       </c>
       <c r="D127" t="n">
         <v>126</v>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2.306706400601063</v>
+        <v>2.306706400601064</v>
       </c>
       <c r="D129" t="n">
         <v>128</v>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2.306931397631996</v>
+        <v>2.306931397631997</v>
       </c>
       <c r="D130" t="n">
         <v>129</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2.317775570522614</v>
+        <v>2.317775570522615</v>
       </c>
       <c r="D131" t="n">
         <v>130</v>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2.326024631400954</v>
+        <v>2.326024631400955</v>
       </c>
       <c r="D134" t="n">
         <v>133</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2.326577164822367</v>
+        <v>2.326577164822365</v>
       </c>
       <c r="D135" t="n">
         <v>134</v>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>2.327800757639896</v>
+        <v>2.327800757639897</v>
       </c>
       <c r="D136" t="n">
         <v>135</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2.342738156704757</v>
+        <v>2.342738156704758</v>
       </c>
       <c r="D139" t="n">
         <v>138</v>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2.347629236282947</v>
+        <v>2.347629236282949</v>
       </c>
       <c r="D140" t="n">
         <v>139</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2.354701135242428</v>
+        <v>2.354701135242429</v>
       </c>
       <c r="D142" t="n">
         <v>141</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2.355437518210778</v>
+        <v>2.355437518210779</v>
       </c>
       <c r="D143" t="n">
         <v>142</v>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2.35742806758786</v>
+        <v>2.357428067587861</v>
       </c>
       <c r="D144" t="n">
         <v>143</v>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2.360653385828175</v>
+        <v>2.360653385828176</v>
       </c>
       <c r="D145" t="n">
         <v>144</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2.362303663218555</v>
+        <v>2.362303663218557</v>
       </c>
       <c r="D146" t="n">
         <v>145</v>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>2.382019409392692</v>
+        <v>2.382019409392693</v>
       </c>
       <c r="D150" t="n">
         <v>149</v>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>2.385773459994635</v>
+        <v>2.385773459994636</v>
       </c>
       <c r="D151" t="n">
         <v>150</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2.393307037852836</v>
+        <v>2.393307037852837</v>
       </c>
       <c r="D152" t="n">
         <v>151</v>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>2.428389608256134</v>
+        <v>2.428389608256135</v>
       </c>
       <c r="D157" t="n">
         <v>156</v>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>2.428769770649007</v>
+        <v>2.428769770649006</v>
       </c>
       <c r="D158" t="n">
         <v>157</v>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2.435446972553423</v>
+        <v>2.435446972553424</v>
       </c>
       <c r="D159" t="n">
         <v>158</v>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>2.445950551269787</v>
+        <v>2.445950551269788</v>
       </c>
       <c r="D160" t="n">
         <v>159</v>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2.455818527721652</v>
+        <v>2.455818527721654</v>
       </c>
       <c r="D163" t="n">
         <v>162</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2.461721010099457</v>
+        <v>2.461721010099459</v>
       </c>
       <c r="D164" t="n">
         <v>163</v>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2.467925848234416</v>
+        <v>2.467925848234417</v>
       </c>
       <c r="D165" t="n">
         <v>164</v>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>2.468161441532856</v>
+        <v>2.468161441532857</v>
       </c>
       <c r="D166" t="n">
         <v>165</v>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>2.483122943432949</v>
+        <v>2.48312294343295</v>
       </c>
       <c r="D167" t="n">
         <v>166</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2.511844681103095</v>
+        <v>2.511844681103097</v>
       </c>
       <c r="D168" t="n">
         <v>167</v>
@@ -3159,7 +3159,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>2.521485384160801</v>
+        <v>2.521485384160802</v>
       </c>
       <c r="D171" t="n">
         <v>170</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>2.523457310390944</v>
+        <v>2.523457310390945</v>
       </c>
       <c r="D172" t="n">
         <v>171</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2.535023427331285</v>
+        <v>2.535023427331286</v>
       </c>
       <c r="D173" t="n">
         <v>172</v>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2.53630204743449</v>
+        <v>2.536302047434489</v>
       </c>
       <c r="D175" t="n">
         <v>174</v>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2.567269894938152</v>
+        <v>2.567269894938151</v>
       </c>
       <c r="D180" t="n">
         <v>179</v>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2.58173120276074</v>
+        <v>2.581731202760742</v>
       </c>
       <c r="D183" t="n">
         <v>182</v>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>2.66358572557284</v>
+        <v>2.663585725572841</v>
       </c>
       <c r="D189" t="n">
         <v>188</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>2.695410281693217</v>
+        <v>2.695410281693218</v>
       </c>
       <c r="D190" t="n">
         <v>189</v>
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>2.76122785331315</v>
+        <v>2.761227853313151</v>
       </c>
       <c r="D196" t="n">
         <v>195</v>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>2.767658466815638</v>
+        <v>2.767658466815639</v>
       </c>
       <c r="D198" t="n">
         <v>197</v>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>2.778773550497863</v>
+        <v>2.778773550497865</v>
       </c>
       <c r="D199" t="n">
         <v>198</v>
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>2.784087022393352</v>
+        <v>2.784087022393351</v>
       </c>
       <c r="D200" t="n">
         <v>199</v>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>2.811599330696371</v>
+        <v>2.811599330696372</v>
       </c>
       <c r="D202" t="n">
         <v>201</v>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>2.817942104020186</v>
+        <v>2.817942104020187</v>
       </c>
       <c r="D203" t="n">
         <v>202</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>2.824428254541614</v>
+        <v>2.824428254541615</v>
       </c>
       <c r="D205" t="n">
         <v>204</v>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>2.850039865917742</v>
+        <v>2.850039865917743</v>
       </c>
       <c r="D206" t="n">
         <v>205</v>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>2.878619916005815</v>
+        <v>2.878619916005816</v>
       </c>
       <c r="D208" t="n">
         <v>207</v>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>2.926815662450544</v>
+        <v>2.926815662450545</v>
       </c>
       <c r="D210" t="n">
         <v>209</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>2.931375062218854</v>
+        <v>2.931375062218855</v>
       </c>
       <c r="D211" t="n">
         <v>210</v>
@@ -3815,7 +3815,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>2.954882287793785</v>
+        <v>2.954882287793787</v>
       </c>
       <c r="D212" t="n">
         <v>211</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>2.992297397362443</v>
+        <v>2.992297397362445</v>
       </c>
       <c r="D217" t="n">
         <v>216</v>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>3.007977987695615</v>
+        <v>3.007977987695614</v>
       </c>
       <c r="D218" t="n">
         <v>217</v>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>3.010180697508016</v>
+        <v>3.010180697508017</v>
       </c>
       <c r="D219" t="n">
         <v>218</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>3.035111321170719</v>
+        <v>3.035111321170717</v>
       </c>
       <c r="D220" t="n">
         <v>219</v>
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>3.037279593619371</v>
+        <v>3.037279593619372</v>
       </c>
       <c r="D221" t="n">
         <v>220</v>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>3.052385339417484</v>
+        <v>3.052385339417486</v>
       </c>
       <c r="D222" t="n">
         <v>221</v>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>3.053044720706486</v>
+        <v>3.053044720706488</v>
       </c>
       <c r="D223" t="n">
         <v>222</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>3.09275938411877</v>
+        <v>3.092759384118771</v>
       </c>
       <c r="D224" t="n">
         <v>223</v>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>3.162325813413912</v>
+        <v>3.162325813413913</v>
       </c>
       <c r="D227" t="n">
         <v>226</v>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>3.162333285011525</v>
+        <v>3.162333285011526</v>
       </c>
       <c r="D228" t="n">
         <v>227</v>
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>3.232749633922047</v>
+        <v>3.232749633922049</v>
       </c>
       <c r="D232" t="n">
         <v>231</v>
